--- a/product_selector_out/STM32F4 series - diff.xlsx
+++ b/product_selector_out/STM32F4 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$439</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$409</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E439"/>
+  <dimension ref="A1:E409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9495</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="18">
@@ -1403,22 +1403,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1430,29 +1426,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1462,116 +1454,112 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>106 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -1583,18 +1571,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -1606,34 +1594,30 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1651,16 +1635,16 @@
           <t>161</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1670,7 +1654,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1678,50 +1662,54 @@
           <t>161</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -1733,18 +1721,18 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -1756,18 +1744,18 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -1779,88 +1767,76 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F479VG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F479VG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1883,7 +1859,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1906,87 +1882,99 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -1998,18 +1986,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2021,150 +2009,162 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQPF144</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>LQFP 144 20x20x1.4 mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>LQPF144</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>LQPF144</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2176,22 +2176,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2203,137 +2199,117 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469ZG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469ZG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469VG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469VG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F479NG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2356,7 +2332,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F479NG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2379,169 +2355,145 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469ZI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469ZI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479VI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2564,7 +2516,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479VI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2587,134 +2539,134 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479ZI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2737,7 +2689,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479ZI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2760,7 +2712,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F479NI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2783,7 +2735,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F479NI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2806,7 +2758,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2816,12 +2768,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -2833,7 +2785,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2843,12 +2795,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -2860,7 +2812,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2870,12 +2822,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -2887,134 +2839,134 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3037,7 +2989,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3060,53 +3012,61 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3116,7 +3076,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3124,104 +3084,108 @@
           <t>UFBGA169, WLCSP168</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>128 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -3233,34 +3197,30 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3270,24 +3230,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3297,105 +3257,97 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>106 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3418,7 +3370,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3441,7 +3393,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3468,7 +3420,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3495,7 +3447,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3522,7 +3474,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3545,7 +3497,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3568,22 +3520,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -3595,22 +3547,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -3622,22 +3574,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
+          <t>128 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -3649,7 +3601,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3672,7 +3624,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3695,22 +3647,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -3722,22 +3674,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -3749,22 +3701,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -3776,7 +3728,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3799,7 +3751,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3822,22 +3774,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -3849,22 +3801,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -3876,22 +3828,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
+          <t>159 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
@@ -3903,61 +3855,53 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3967,162 +3911,158 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>128 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32F469NE</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32F469NE</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32F469NE</t>
+          <t>STM32F411VC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32F469NE</t>
+          <t>STM32F411VC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -4134,18 +4074,18 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32F469NE</t>
+          <t>STM32F411RC</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -4157,18 +4097,18 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32F479II</t>
+          <t>STM32F411RC</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -4180,18 +4120,18 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32F479II</t>
+          <t>STM32F411CC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -4203,88 +4143,76 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32F479BI</t>
+          <t>STM32F411CC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32F479BI</t>
+          <t>STM32F411VE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32F479BI</t>
+          <t>STM32F411VE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32F479BI</t>
+          <t>STM32F411CE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4307,7 +4235,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32F479BI</t>
+          <t>STM32F411CE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4330,226 +4258,214 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32F479AI</t>
+          <t>STM32F411RE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32F479AI</t>
+          <t>STM32F411RE</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32F479AI</t>
+          <t>STM32F407VG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>128 (workbook and API agree)</t>
+          <t>Ethernet||SD/MMC</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32F479AI</t>
+          <t>STM32F407VG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Ethernet, SD/MMC</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32F479AI</t>
+          <t>STM32F407VG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ethernet||SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32F469IE</t>
+          <t>STM32F407VG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32F469IE</t>
+          <t>STM32F407VG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32F469IE</t>
+          <t>STM32F417VE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
-        </is>
-      </c>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32F469IE</t>
+          <t>STM32F417VE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
@@ -4561,18 +4477,18 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32F469IE</t>
+          <t>STM32F417VG</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -4584,122 +4500,122 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32F469BE</t>
+          <t>STM32F417VG</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32F469BE</t>
+          <t>STM32F407ZE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>Ethernet||SD/MMC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32F469BE</t>
+          <t>STM32F407ZE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>Ethernet, SD/MMC</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E179" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32F469BE</t>
+          <t>STM32F407ZE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ethernet||SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32F469BE</t>
+          <t>STM32F407ZE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -4711,122 +4627,122 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32F469BI</t>
+          <t>STM32F407ZE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32F469BI</t>
+          <t>STM32F407VE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>Ethernet||SD/MMC</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E183" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32F469BI</t>
+          <t>STM32F407VE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>Ethernet, SD/MMC</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E184" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32F469BI</t>
+          <t>STM32F407VE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ethernet||SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32F469BI</t>
+          <t>STM32F407VE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -4838,18 +4754,18 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32F411VC</t>
+          <t>STM32F407VE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
@@ -4861,18 +4777,18 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32F411VC</t>
+          <t>STM32F417ZG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -4884,18 +4800,18 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32F411RC</t>
+          <t>STM32F417ZG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -4907,76 +4823,88 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32F411RC</t>
+          <t>STM32F407IE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ethernet||SD/MMC</t>
+        </is>
+      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32F411CC</t>
+          <t>STM32F407IE</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ethernet, SD/MMC</t>
+        </is>
+      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32F411CC</t>
+          <t>STM32F407IE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ethernet||SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32F411VE</t>
+          <t>STM32F407IE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4999,7 +4927,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32F411VE</t>
+          <t>STM32F407IE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5022,7 +4950,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32F411CE</t>
+          <t>STM32F417ZE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5045,7 +4973,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32F411CE</t>
+          <t>STM32F417ZE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5068,53 +4996,61 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32F411RE</t>
+          <t>STM32F407ZG</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ethernet||SD/MMC</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32F411RE</t>
+          <t>STM32F407ZG</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ethernet, SD/MMC</t>
+        </is>
+      </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32F407VG</t>
+          <t>STM32F407ZG</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5124,7 +5060,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ethernet||SD/MMC</t>
+          <t>Ethernet||SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5132,70 +5068,62 @@
           <t>Ethernet, Parallel camera interface, SD/MMC</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32F407VG</t>
+          <t>STM32F407ZG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Ethernet, SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E200" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32F407VG</t>
+          <t>STM32F407ZG</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E201" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32F407VG</t>
+          <t>STM32F417IG</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5218,7 +5146,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32F407VG</t>
+          <t>STM32F417IG</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5241,7 +5169,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32F417VE</t>
+          <t>STM32F417IE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5264,7 +5192,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32F417VE</t>
+          <t>STM32F417IE</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5287,53 +5215,61 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32F417VG</t>
+          <t>STM32F407IG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Ethernet||SD/MMC</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32F417VG</t>
+          <t>STM32F407IG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Ethernet, SD/MMC</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Ethernet, Parallel camera interface, SD/MMC</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32F407ZE</t>
+          <t>STM32F407IG</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5343,7 +5279,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ethernet||SD/MMC</t>
+          <t>Ethernet||SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5351,70 +5287,62 @@
           <t>Ethernet, Parallel camera interface, SD/MMC</t>
         </is>
       </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32F407ZE</t>
+          <t>STM32F407IG</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Ethernet, SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E209" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32F407ZE</t>
+          <t>STM32F407IG</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E210" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32F407ZE</t>
+          <t>STM32F401CB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5437,7 +5365,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32F407ZE</t>
+          <t>STM32F401CB</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5460,99 +5388,87 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32F407VE</t>
+          <t>STM32F401VE</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32F407VE</t>
+          <t>STM32F401VE</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Ethernet, SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32F407VE</t>
+          <t>STM32F401VB</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32F407VE</t>
+          <t>STM32F401VB</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -5564,18 +5480,18 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32F407VE</t>
+          <t>STM32F401VC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -5587,18 +5503,18 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32F417ZG</t>
+          <t>STM32F401VC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
@@ -5610,18 +5526,18 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32F417ZG</t>
+          <t>STM32F401CC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
@@ -5633,88 +5549,76 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32F407IE</t>
+          <t>STM32F401CC</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32F407IE</t>
+          <t>STM32F401RC</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Ethernet, SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E221" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32F407IE</t>
+          <t>STM32F401RC</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E222" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32F407IE</t>
+          <t>STM32F401RB</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5737,7 +5641,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32F407IE</t>
+          <t>STM32F401RB</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5760,7 +5664,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32F417ZE</t>
+          <t>STM32F401CD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5783,7 +5687,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32F417ZE</t>
+          <t>STM32F401CD</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5806,99 +5710,87 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32F407ZG</t>
+          <t>STM32F401CE</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32F407ZG</t>
+          <t>STM32F401CE</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Ethernet, SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E228" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32F407ZG</t>
+          <t>STM32F401VD</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32F407ZG</t>
+          <t>STM32F401VD</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
@@ -5910,18 +5802,18 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32F407ZG</t>
+          <t>STM32F401RE</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
@@ -5933,18 +5825,18 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32F417IG</t>
+          <t>STM32F401RE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -5956,18 +5848,18 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32F417IG</t>
+          <t>STM32F401RD</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
@@ -5979,18 +5871,18 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32F417IE</t>
+          <t>STM32F401RD</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
@@ -6002,18 +5894,18 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32F417IE</t>
+          <t>STM32F446RC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
@@ -6025,88 +5917,76 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32F407IG</t>
+          <t>STM32F446RC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E236" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>STM32F407IG</t>
+          <t>STM32F446VE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Ethernet, SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E237" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STM32F407IG</t>
+          <t>STM32F446VE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Ethernet||SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Ethernet, Parallel camera interface, SD/MMC</t>
-        </is>
-      </c>
-      <c r="E238" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STM32F407IG</t>
+          <t>STM32F446RE</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6129,7 +6009,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STM32F407IG</t>
+          <t>STM32F446RE</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6152,7 +6032,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>STM32F401CB</t>
+          <t>STM32F446ZE</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6175,7 +6055,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STM32F401CB</t>
+          <t>STM32F446ZE</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6198,7 +6078,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STM32F401VE</t>
+          <t>STM32F446ZC</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6221,7 +6101,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STM32F401VE</t>
+          <t>STM32F446ZC</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6244,7 +6124,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32F401VB</t>
+          <t>STM32F446MC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6267,7 +6147,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32F401VB</t>
+          <t>STM32F446MC</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6290,7 +6170,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32F401VC</t>
+          <t>STM32F446ME</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6313,7 +6193,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32F401VC</t>
+          <t>STM32F446ME</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6336,7 +6216,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>STM32F401CC</t>
+          <t>STM32F446VC</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6359,7 +6239,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>STM32F401CC</t>
+          <t>STM32F446VC</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6382,7 +6262,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>STM32F401RC</t>
+          <t>STM32F427AG</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6405,7 +6285,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>STM32F401RC</t>
+          <t>STM32F427AG</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6428,87 +6308,99 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>STM32F401RB</t>
+          <t>STM32F437AI</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>STM32F401RB</t>
+          <t>STM32F437AI</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>STM32F401CD</t>
+          <t>STM32F437AI</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>130 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E255" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>STM32F401CD</t>
+          <t>STM32F437AI</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
@@ -6520,18 +6412,18 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STM32F401CE</t>
+          <t>STM32F437AI</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
@@ -6543,18 +6435,18 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>STM32F401CE</t>
+          <t>STM32F427AI</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
@@ -6566,18 +6458,18 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>STM32F401VD</t>
+          <t>STM32F427AI</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
@@ -6589,18 +6481,18 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>STM32F401VD</t>
+          <t>STM32F427ZI</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -6612,18 +6504,18 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>STM32F401RE</t>
+          <t>STM32F427ZI</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
@@ -6635,76 +6527,88 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>STM32F401RE</t>
+          <t>STM32F437ZI</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>STM32F401RD</t>
+          <t>STM32F437ZI</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>STM32F401RD</t>
+          <t>STM32F437ZI</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E264" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>STM32F446RC</t>
+          <t>STM32F437ZI</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6727,7 +6631,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>STM32F446RC</t>
+          <t>STM32F437ZI</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6750,7 +6654,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>STM32F446VE</t>
+          <t>STM32F427II</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6773,7 +6677,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>STM32F446VE</t>
+          <t>STM32F427II</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6796,87 +6700,99 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>STM32F446RE</t>
+          <t>STM32F437II</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>STM32F446RE</t>
+          <t>STM32F437II</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E270" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>STM32F446ZE</t>
+          <t>STM32F437II</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>140 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E271" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>STM32F446ZE</t>
+          <t>STM32F437II</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -6888,18 +6804,18 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>STM32F446ZC</t>
+          <t>STM32F437II</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -6911,18 +6827,18 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>STM32F446ZC</t>
+          <t>STM32F427VG</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
@@ -6934,18 +6850,18 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>STM32F446MC</t>
+          <t>STM32F427VG</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -6957,18 +6873,18 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>STM32F446MC</t>
+          <t>STM32F437VG</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -6980,18 +6896,18 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>STM32F446ME</t>
+          <t>STM32F437VG</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -7003,76 +6919,88 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>STM32F446ME</t>
+          <t>STM32F437ZG</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E278" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>STM32F446VC</t>
+          <t>STM32F437ZG</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E279" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>STM32F446VC</t>
+          <t>STM32F437ZG</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E280" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>STM32F427AG</t>
+          <t>STM32F437ZG</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7095,7 +7023,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>STM32F427AG</t>
+          <t>STM32F437ZG</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7118,99 +7046,87 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>STM32F437AI</t>
+          <t>STM32F427ZG</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E283" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>STM32F437AI</t>
+          <t>STM32F427ZG</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E284" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>STM32F437AI</t>
+          <t>STM32F427IG</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>130 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E285" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>STM32F437AI</t>
+          <t>STM32F427IG</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
@@ -7222,76 +7138,88 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>STM32F437AI</t>
+          <t>STM32F437IG</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E287" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>STM32F427AI</t>
+          <t>STM32F437IG</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E288" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>STM32F427AI</t>
+          <t>STM32F437IG</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>140 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E289" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E289" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>STM32F427ZI</t>
+          <t>STM32F437IG</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7314,7 +7242,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>STM32F427ZI</t>
+          <t>STM32F437IG</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7337,99 +7265,87 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>STM32F437ZI</t>
+          <t>STM32F427VI</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
-        </is>
-      </c>
-      <c r="E292" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>STM32F437ZI</t>
+          <t>STM32F427VI</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
-        </is>
-      </c>
-      <c r="E293" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>STM32F437ZI</t>
+          <t>STM32F437VI</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
-        </is>
-      </c>
-      <c r="E294" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>STM32F437ZI</t>
+          <t>STM32F437VI</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
@@ -7441,18 +7357,18 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>STM32F437ZI</t>
+          <t>STM32F412RE</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
@@ -7464,18 +7380,18 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>STM32F427II</t>
+          <t>STM32F412RE</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
@@ -7487,18 +7403,18 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>STM32F427II</t>
+          <t>STM32F412VE</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -7510,88 +7426,76 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>STM32F437II</t>
+          <t>STM32F412VE</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E299" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>STM32F437II</t>
+          <t>STM32F412CE</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E300" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>STM32F437II</t>
+          <t>STM32F412CE</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>140 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E301" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>STM32F437II</t>
+          <t>STM32F412VG</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7614,7 +7518,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>STM32F437II</t>
+          <t>STM32F412VG</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7637,7 +7541,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>STM32F427VG</t>
+          <t>STM32F412CG</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7660,7 +7564,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>STM32F427VG</t>
+          <t>STM32F412CG</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7683,7 +7587,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>STM32F437VG</t>
+          <t>STM32F412ZG</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7706,7 +7610,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>STM32F437VG</t>
+          <t>STM32F412ZG</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7729,99 +7633,87 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>STM32F437ZG</t>
+          <t>STM32F412RG</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
-        </is>
-      </c>
-      <c r="E308" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>STM32F437ZG</t>
+          <t>STM32F412RG</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
-        </is>
-      </c>
-      <c r="E309" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>STM32F437ZG</t>
+          <t>STM32F412ZE</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
-        </is>
-      </c>
-      <c r="E310" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>STM32F437ZG</t>
+          <t>STM32F412ZE</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr">
@@ -7833,18 +7725,18 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>STM32F437ZG</t>
+          <t>STM32F429AG</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
@@ -7856,18 +7748,18 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>STM32F427ZG</t>
+          <t>STM32F429AG</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E313" s="3" t="inlineStr">
@@ -7879,168 +7771,168 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>STM32F427ZG</t>
+          <t>STM32F429ZE</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E314" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>STM32F427IG</t>
+          <t>STM32F429ZE</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E315" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>STM32F427IG</t>
+          <t>STM32F429ZE</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E316" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQFP144, WLCSP143</t>
+        </is>
+      </c>
+      <c r="E316" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>STM32F437IG</t>
+          <t>STM32F429ZE</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E317" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>STM32F437IG</t>
+          <t>STM32F429ZE</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E318" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>STM32F437IG</t>
+          <t>STM32F429IE</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>140 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E319" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>STM32F437IG</t>
+          <t>STM32F429IE</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -8052,18 +7944,18 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>STM32F437IG</t>
+          <t>STM32F429VE</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -8075,18 +7967,18 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>STM32F427VI</t>
+          <t>STM32F429VE</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
@@ -8098,18 +7990,18 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>STM32F427VI</t>
+          <t>STM32F439BI</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E323" s="3" t="inlineStr">
@@ -8121,18 +8013,18 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>STM32F437VI</t>
+          <t>STM32F439BI</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
@@ -8144,18 +8036,18 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>STM32F437VI</t>
+          <t>STM32F429NI</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -8167,18 +8059,18 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>STM32F412RE</t>
+          <t>STM32F429NI</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -8190,18 +8082,18 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>STM32F412RE</t>
+          <t>STM32F439NI</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E327" s="3" t="inlineStr">
@@ -8213,18 +8105,18 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>STM32F412VE</t>
+          <t>STM32F439NI</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
@@ -8236,18 +8128,18 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>STM32F412VE</t>
+          <t>STM32F429BE</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E329" s="3" t="inlineStr">
@@ -8259,18 +8151,18 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>STM32F412CE</t>
+          <t>STM32F429BE</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
@@ -8282,18 +8174,18 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>STM32F412CE</t>
+          <t>STM32F429NE</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E331" s="3" t="inlineStr">
@@ -8305,18 +8197,18 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>STM32F412VG</t>
+          <t>STM32F429NE</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
@@ -8328,76 +8220,88 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>STM32F412VG</t>
+          <t>STM32F439IG</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E333" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>STM32F412CG</t>
+          <t>STM32F439IG</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E334" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>STM32F412CG</t>
+          <t>STM32F439IG</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>140 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E335" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E335" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>STM32F412ZG</t>
+          <t>STM32F439IG</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -8420,7 +8324,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>STM32F412ZG</t>
+          <t>STM32F439IG</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -8443,7 +8347,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>STM32F412RG</t>
+          <t>STM32F429IG</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -8466,7 +8370,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>STM32F412RG</t>
+          <t>STM32F429IG</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -8489,7 +8393,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>STM32F412ZE</t>
+          <t>STM32F429VG</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -8512,7 +8416,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>STM32F412ZE</t>
+          <t>STM32F429VG</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -8535,7 +8439,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>STM32F429AG</t>
+          <t>STM32F429ZI</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8558,7 +8462,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>STM32F429AG</t>
+          <t>STM32F429ZI</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8581,22 +8485,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>STM32F429ZE</t>
+          <t>STM32F439AI</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E344" s="4" t="inlineStr">
@@ -8608,22 +8512,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>STM32F429ZE</t>
+          <t>STM32F439AI</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E345" s="5" t="inlineStr">
@@ -8635,22 +8539,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>STM32F429ZE</t>
+          <t>STM32F439AI</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
+          <t>130 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>LQFP144, WLCSP143</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E346" s="6" t="inlineStr">
@@ -8662,7 +8566,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>STM32F429ZE</t>
+          <t>STM32F439AI</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -8685,7 +8589,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>STM32F429ZE</t>
+          <t>STM32F439AI</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8708,7 +8612,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>STM32F429IE</t>
+          <t>STM32F429AI</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8731,7 +8635,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>STM32F429IE</t>
+          <t>STM32F429AI</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8754,7 +8658,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>STM32F429VE</t>
+          <t>STM32F429VI</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8777,7 +8681,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>STM32F429VE</t>
+          <t>STM32F429VI</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8800,7 +8704,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>STM32F439BI</t>
+          <t>STM32F439BG</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8823,7 +8727,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>STM32F439BI</t>
+          <t>STM32F439BG</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -8846,7 +8750,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>STM32F429NI</t>
+          <t>STM32F429BG</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8869,7 +8773,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>STM32F429NI</t>
+          <t>STM32F429BG</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -8892,7 +8796,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>STM32F439NI</t>
+          <t>STM32F439NG</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8915,7 +8819,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>STM32F439NI</t>
+          <t>STM32F439NG</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8938,7 +8842,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>STM32F429BE</t>
+          <t>STM32F429NG</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8961,7 +8865,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>STM32F429BE</t>
+          <t>STM32F429NG</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8984,7 +8888,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>STM32F429NE</t>
+          <t>STM32F439ZG</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -9007,7 +8911,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>STM32F429NE</t>
+          <t>STM32F439ZG</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -9030,99 +8934,87 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>STM32F439IG</t>
+          <t>STM32F429ZG</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E363" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>STM32F439IG</t>
+          <t>STM32F429ZG</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E364" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>STM32F439IG</t>
+          <t>STM32F439VG</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>140 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E365" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>STM32F439IG</t>
+          <t>STM32F439VG</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
@@ -9134,18 +9026,18 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>STM32F439IG</t>
+          <t>STM32F429BI</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E367" s="3" t="inlineStr">
@@ -9157,18 +9049,18 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>STM32F429IG</t>
+          <t>STM32F429BI</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
@@ -9180,18 +9072,18 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>STM32F429IG</t>
+          <t>STM32F429II</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E369" s="3" t="inlineStr">
@@ -9203,18 +9095,18 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>STM32F429VG</t>
+          <t>STM32F429II</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
@@ -9226,168 +9118,168 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>STM32F429VG</t>
+          <t>STM32F439II</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E371" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E371" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>STM32F429ZI</t>
+          <t>STM32F439II</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E372" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>STM32F429ZI</t>
+          <t>STM32F439II</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>140 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E373" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E373" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>STM32F439AI</t>
+          <t>STM32F439II</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E374" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>STM32F439AI</t>
+          <t>STM32F439II</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E375" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>STM32F439AI</t>
+          <t>STM32F439ZI</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>130 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E376" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E376" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>STM32F439AI</t>
+          <t>STM32F439ZI</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E377" s="3" t="inlineStr">
@@ -9399,18 +9291,18 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>STM32F439AI</t>
+          <t>STM32F439VI</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
@@ -9422,18 +9314,18 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>STM32F429AI</t>
+          <t>STM32F439VI</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
@@ -9445,18 +9337,18 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>STM32F429AI</t>
+          <t>STM32F423RH</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
@@ -9468,18 +9360,18 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>STM32F429VI</t>
+          <t>STM32F423RH</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E381" s="3" t="inlineStr">
@@ -9491,18 +9383,18 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>STM32F429VI</t>
+          <t>STM32F413RH</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
@@ -9514,18 +9406,18 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>STM32F439BG</t>
+          <t>STM32F413RH</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E383" s="3" t="inlineStr">
@@ -9537,18 +9429,18 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>STM32F439BG</t>
+          <t>STM32F423VH</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
@@ -9560,18 +9452,18 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>STM32F429BG</t>
+          <t>STM32F423VH</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E385" s="3" t="inlineStr">
@@ -9583,18 +9475,18 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>STM32F429BG</t>
+          <t>STM32F423MH</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
@@ -9606,18 +9498,18 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>STM32F439NG</t>
+          <t>STM32F423MH</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E387" s="3" t="inlineStr">
@@ -9629,18 +9521,18 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>STM32F439NG</t>
+          <t>STM32F413ZH</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
@@ -9652,18 +9544,18 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>STM32F429NG</t>
+          <t>STM32F413ZH</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E389" s="3" t="inlineStr">
@@ -9675,18 +9567,18 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>STM32F429NG</t>
+          <t>STM32F413CH</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
@@ -9698,18 +9590,18 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>STM32F439ZG</t>
+          <t>STM32F413CH</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E391" s="3" t="inlineStr">
@@ -9721,18 +9613,18 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>STM32F439ZG</t>
+          <t>STM32F413VH</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
@@ -9744,18 +9636,18 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>STM32F429ZG</t>
+          <t>STM32F413VH</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E393" s="3" t="inlineStr">
@@ -9767,18 +9659,18 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>STM32F429ZG</t>
+          <t>STM32F413RG</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
@@ -9790,18 +9682,18 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>STM32F439VG</t>
+          <t>STM32F413RG</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E395" s="3" t="inlineStr">
@@ -9813,18 +9705,18 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>STM32F439VG</t>
+          <t>STM32F413ZG</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
@@ -9836,18 +9728,18 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>STM32F429BI</t>
+          <t>STM32F413ZG</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E397" s="3" t="inlineStr">
@@ -9859,18 +9751,18 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>STM32F429BI</t>
+          <t>STM32F413VG</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
@@ -9882,18 +9774,18 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>STM32F429II</t>
+          <t>STM32F413VG</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E399" s="3" t="inlineStr">
@@ -9905,18 +9797,18 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>STM32F429II</t>
+          <t>STM32F423CH</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
@@ -9928,88 +9820,76 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>STM32F439II</t>
+          <t>STM32F423CH</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E401" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>STM32F439II</t>
+          <t>STM32F413MG</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E402" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>STM32F439II</t>
+          <t>STM32F413MG</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>140 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E403" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>STM32F439II</t>
+          <t>STM32F423ZH</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -10032,7 +9912,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>STM32F439II</t>
+          <t>STM32F423ZH</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -10055,7 +9935,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>STM32F439ZI</t>
+          <t>STM32F413CG</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -10078,7 +9958,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>STM32F439ZI</t>
+          <t>STM32F413CG</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -10101,7 +9981,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>STM32F439VI</t>
+          <t>STM32F413MH</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -10124,7 +10004,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>STM32F439VI</t>
+          <t>STM32F413MH</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -10144,698 +10024,8 @@
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>STM32F423RH</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E410" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>STM32F423RH</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E411" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>STM32F413RH</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E412" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>STM32F413RH</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E413" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>STM32F423VH</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E414" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>STM32F423VH</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E415" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>STM32F423MH</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr"/>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E416" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>STM32F423MH</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E417" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>STM32F413ZH</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr"/>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E418" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>STM32F413ZH</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E419" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>STM32F413CH</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E420" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>STM32F413CH</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E421" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>STM32F413VH</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E422" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>STM32F413VH</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E423" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>STM32F413RG</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr"/>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E424" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>STM32F413RG</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E425" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>STM32F413ZG</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E426" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>STM32F413ZG</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E427" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>STM32F413VG</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E428" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>STM32F413VG</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E429" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>STM32F423CH</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E430" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>STM32F423CH</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E431" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>STM32F413MG</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E432" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>STM32F413MG</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E433" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>STM32F423ZH</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E434" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>STM32F423ZH</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E435" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>STM32F413CG</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E436" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>STM32F413CG</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E437" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>STM32F413MH</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E438" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>STM32F413MH</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E439" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E439"/>
+  <autoFilter ref="A18:E409"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F4 series - diff.xlsx
+++ b/product_selector_out/STM32F4 series - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9834</v>
+        <v>9983</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9505</v>
+        <v>9654</v>
       </c>
     </row>
     <row r="18">
